--- a/03_Outputs/Rio_Grande/10_Seguridad/seguridad.xlsx
+++ b/03_Outputs/Rio_Grande/10_Seguridad/seguridad.xlsx
@@ -19,20 +19,22 @@
     <sheet name="P6_cambio_municipio" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="irv" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="desaparecidos" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="_fig_01" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="_fig_02" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="_fig_03" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="_fig_04" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="_fig_05" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="_mapa10_homicidios" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="_mapa10_homicidios_dpto" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="reparacion_colectiva" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="reparacion_colectiva_sujetos" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="_fig_01" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="_fig_02" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="_fig_03" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="_fig_04" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="_fig_05" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="_mapa10_homicidios" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="_mapa10_homicidios_dpto" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="65">
+  <numFmts count="73">
     <numFmt numFmtId="165" formatCode="#,##0.00"/>
     <numFmt numFmtId="166" formatCode="0.00%"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
@@ -98,8 +100,16 @@
     <numFmt numFmtId="227" formatCode="#,##0"/>
     <numFmt numFmtId="228" formatCode="0.0%"/>
     <numFmt numFmtId="229" formatCode="0.0%"/>
+    <numFmt numFmtId="230" formatCode="#,##0"/>
+    <numFmt numFmtId="231" formatCode="#,##0"/>
+    <numFmt numFmtId="232" formatCode="#,##0"/>
+    <numFmt numFmtId="233" formatCode="#,##0"/>
+    <numFmt numFmtId="234" formatCode="0.0%"/>
+    <numFmt numFmtId="235" formatCode="0.0%"/>
+    <numFmt numFmtId="236" formatCode="0.0%"/>
+    <numFmt numFmtId="237" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -109,23 +119,296 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="24">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -145,7 +428,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0"/>
     <xf applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0"/>
@@ -153,68 +436,125 @@
     <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0"/>
     <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="166" xfId="0"/>
     <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="167" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="168" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="169" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="170" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="171" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="172" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="168" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="169" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="170" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="171" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="172" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="173" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="174" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="174" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="175" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="176" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="176" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="177" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="178" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="178" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="179" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="180" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="180" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="5" fontId="7" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="181" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="182" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="182" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="183" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="184" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="184" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="185" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="186" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="186" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="187" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="188" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="188" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="189" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="190" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="190" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="6" fontId="9" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="191" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="192" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="7" fontId="10" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="193" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="194" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="11" numFmtId="194" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="195" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="196" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="11" numFmtId="196" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="197" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="198" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="11" numFmtId="198" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="8" fontId="12" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="199" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="200" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="13" numFmtId="200" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="201" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="202" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="13" numFmtId="202" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="203" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="204" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="13" numFmtId="204" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="9" fontId="14" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="205" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="206" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="207" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="208" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="209" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="10" fontId="15" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="210" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="211" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="212" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="213" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="214" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="11" fontId="16" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="215" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="216" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="217" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="218" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="219" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="17" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="12" fontId="17" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="220" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="221" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="222" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="223" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="224" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="18" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="13" fontId="18" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="225" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="19" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="14" fontId="19" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="20" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="226" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="227" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="20" numFmtId="227" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="228" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="229" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="20" numFmtId="229" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="21" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="15" fontId="21" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="22" numFmtId="0" xfId="0"/>
+    <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="230" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="22" numFmtId="231" xfId="0"/>
+    <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="232" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="22" numFmtId="233" xfId="0"/>
+    <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="234" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="22" numFmtId="235" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="23" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="16" fontId="23" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" applyNumberFormat="1" borderId="0" fillId="16" fontId="23" numFmtId="236" xfId="0"/>
+    <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="237" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="24" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="17" fontId="24" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="25" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="18" fontId="25" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="26" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="19" fontId="26" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="27" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="20" fontId="27" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="28" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="21" fontId="28" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="29" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="22" fontId="29" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="30" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="23" fontId="30" numFmtId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -543,12 +883,12 @@
   <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="5" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="45.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="5" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="34.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="46.711"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -631,46 +971,47 @@
   <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="5" max="6" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="76" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="76" t="inlineStr">
         <is>
           <t>Periodo</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="76" t="inlineStr">
         <is>
           <t>N respuestas</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="76" t="inlineStr">
         <is>
           <t>Muy seguro (%)</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="76" t="inlineStr">
         <is>
           <t>Seguro (%)</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="76" t="inlineStr">
         <is>
           <t>Inseguro (%)</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="76" t="inlineStr">
         <is>
           <t>Muy inseguro (%)</t>
         </is>
@@ -687,19 +1028,19 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="C2" s="58">
+      <c r="C2" s="81">
         <v>344</v>
       </c>
-      <c r="D2" s="54">
+      <c r="D2" s="77">
         <v>0.0709119776858088</v>
       </c>
-      <c r="E2" s="55">
+      <c r="E2" s="78">
         <v>0.568952987569571</v>
       </c>
-      <c r="F2" s="56">
+      <c r="F2" s="79">
         <v>0.258066916691138</v>
       </c>
-      <c r="G2" s="57">
+      <c r="G2" s="80">
         <v>0.102068118053482</v>
       </c>
     </row>
@@ -714,19 +1055,19 @@
           <t>2019 (1)</t>
         </is>
       </c>
-      <c r="C3" s="58">
+      <c r="C3" s="81">
         <v>344</v>
       </c>
-      <c r="D3" s="54">
+      <c r="D3" s="77">
         <v>0.110026323719227</v>
       </c>
-      <c r="E3" s="55">
+      <c r="E3" s="78">
         <v>0.638375585902372</v>
       </c>
-      <c r="F3" s="56">
+      <c r="F3" s="79">
         <v>0.208039147100188</v>
       </c>
-      <c r="G3" s="57">
+      <c r="G3" s="80">
         <v>0.0435589432782132</v>
       </c>
     </row>
@@ -741,19 +1082,19 @@
           <t>2019 (2)</t>
         </is>
       </c>
-      <c r="C4" s="58">
+      <c r="C4" s="81">
         <v>336</v>
       </c>
-      <c r="D4" s="54">
+      <c r="D4" s="77">
         <v>0.0968497273682837</v>
       </c>
-      <c r="E4" s="55">
+      <c r="E4" s="78">
         <v>0.694391114553894</v>
       </c>
-      <c r="F4" s="56">
+      <c r="F4" s="79">
         <v>0.168463820658172</v>
       </c>
-      <c r="G4" s="57">
+      <c r="G4" s="80">
         <v>0.0402953374196502</v>
       </c>
     </row>
@@ -768,19 +1109,19 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="C5" s="58">
+      <c r="C5" s="81">
         <v>216</v>
       </c>
-      <c r="D5" s="54">
+      <c r="D5" s="77">
         <v>0.0506475683150735</v>
       </c>
-      <c r="E5" s="55">
+      <c r="E5" s="78">
         <v>0.696174020100695</v>
       </c>
-      <c r="F5" s="56">
+      <c r="F5" s="79">
         <v>0.206430029843191</v>
       </c>
-      <c r="G5" s="57">
+      <c r="G5" s="80">
         <v>0.0467483817410409</v>
       </c>
     </row>
@@ -795,19 +1136,19 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="C6" s="58">
+      <c r="C6" s="81">
         <v>272</v>
       </c>
-      <c r="D6" s="54">
+      <c r="D6" s="77">
         <v>0.0773599396187067</v>
       </c>
-      <c r="E6" s="55">
+      <c r="E6" s="78">
         <v>0.761660428482399</v>
       </c>
-      <c r="F6" s="56">
+      <c r="F6" s="79">
         <v>0.138086208991511</v>
       </c>
-      <c r="G6" s="57">
+      <c r="G6" s="80">
         <v>0.0228934229073834</v>
       </c>
     </row>
@@ -822,19 +1163,19 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="C7" s="58">
+      <c r="C7" s="81">
         <v>272</v>
       </c>
-      <c r="D7" s="54">
+      <c r="D7" s="77">
         <v>0.122530769984082</v>
       </c>
-      <c r="E7" s="55">
+      <c r="E7" s="78">
         <v>0.646896535699251</v>
       </c>
-      <c r="F7" s="56">
+      <c r="F7" s="79">
         <v>0.184575163012394</v>
       </c>
-      <c r="G7" s="57">
+      <c r="G7" s="80">
         <v>0.0459975313042729</v>
       </c>
     </row>
@@ -849,19 +1190,19 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="C8" s="58">
+      <c r="C8" s="81">
         <v>240</v>
       </c>
-      <c r="D8" s="54">
+      <c r="D8" s="77">
         <v>0.0850803388362212</v>
       </c>
-      <c r="E8" s="55">
+      <c r="E8" s="78">
         <v>0.675680791164399</v>
       </c>
-      <c r="F8" s="56">
+      <c r="F8" s="79">
         <v>0.205778697238382</v>
       </c>
-      <c r="G8" s="57">
+      <c r="G8" s="80">
         <v>0.0334601727609976</v>
       </c>
     </row>
@@ -876,19 +1217,19 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="C9" s="58">
+      <c r="C9" s="81">
         <v>249</v>
       </c>
-      <c r="D9" s="54">
+      <c r="D9" s="77">
         <v>0.0770187542355022</v>
       </c>
-      <c r="E9" s="55">
+      <c r="E9" s="78">
         <v>0.714033165981444</v>
       </c>
-      <c r="F9" s="56">
+      <c r="F9" s="79">
         <v>0.176907170989814</v>
       </c>
-      <c r="G9" s="57">
+      <c r="G9" s="80">
         <v>0.0320409087932396</v>
       </c>
     </row>
@@ -904,45 +1245,47 @@
   <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
-    <col min="4" max="6" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="83" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="83" t="inlineStr">
         <is>
           <t>Periodo</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="83" t="inlineStr">
         <is>
           <t>N respuestas</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="83" t="inlineStr">
         <is>
           <t>Más seguro (%)</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="83" t="inlineStr">
         <is>
           <t>Menos seguro (%)</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="83" t="inlineStr">
         <is>
           <t>Igual (%)</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="83" t="inlineStr">
         <is>
           <t>No sabe/No responde (%)</t>
         </is>
@@ -959,19 +1302,19 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="C2" s="63">
+      <c r="C2" s="88">
         <v>344</v>
       </c>
-      <c r="D2" s="59">
+      <c r="D2" s="84">
         <v>0.176314482754761</v>
       </c>
-      <c r="E2" s="60">
+      <c r="E2" s="85">
         <v>0.193762546944013</v>
       </c>
-      <c r="F2" s="61">
+      <c r="F2" s="86">
         <v>0.617257757966248</v>
       </c>
-      <c r="G2" s="62">
+      <c r="G2" s="87">
         <v>0.0126652123349779</v>
       </c>
     </row>
@@ -986,19 +1329,19 @@
           <t>2019 (1)</t>
         </is>
       </c>
-      <c r="C3" s="63">
+      <c r="C3" s="88">
         <v>344</v>
       </c>
-      <c r="D3" s="59">
+      <c r="D3" s="84">
         <v>0.278560355464205</v>
       </c>
-      <c r="E3" s="60">
+      <c r="E3" s="85">
         <v>0.167363939224072</v>
       </c>
-      <c r="F3" s="61">
+      <c r="F3" s="86">
         <v>0.514827646802668</v>
       </c>
-      <c r="G3" s="62">
+      <c r="G3" s="87">
         <v>0.0392480585090547</v>
       </c>
     </row>
@@ -1013,19 +1356,19 @@
           <t>2019 (2)</t>
         </is>
       </c>
-      <c r="C4" s="63">
+      <c r="C4" s="88">
         <v>336</v>
       </c>
-      <c r="D4" s="59">
+      <c r="D4" s="84">
         <v>0.233565166922982</v>
       </c>
-      <c r="E4" s="60">
+      <c r="E4" s="85">
         <v>0.153541409122006</v>
       </c>
-      <c r="F4" s="61">
+      <c r="F4" s="86">
         <v>0.604812101060503</v>
       </c>
-      <c r="G4" s="62">
+      <c r="G4" s="87">
         <v>0.00808132289450913</v>
       </c>
     </row>
@@ -1040,19 +1383,19 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="C5" s="63">
+      <c r="C5" s="88">
         <v>216</v>
       </c>
-      <c r="D5" s="59">
+      <c r="D5" s="84">
         <v>0.140066275502638</v>
       </c>
-      <c r="E5" s="60">
+      <c r="E5" s="85">
         <v>0.132002665109143</v>
       </c>
-      <c r="F5" s="61">
+      <c r="F5" s="86">
         <v>0.726429348817849</v>
       </c>
-      <c r="G5" s="62">
+      <c r="G5" s="87">
         <v>0.00150171057037049</v>
       </c>
     </row>
@@ -1067,19 +1410,19 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="C6" s="63">
+      <c r="C6" s="88">
         <v>272</v>
       </c>
-      <c r="D6" s="59">
+      <c r="D6" s="84">
         <v>0.134515076855215</v>
       </c>
-      <c r="E6" s="60">
+      <c r="E6" s="85">
         <v>0.119725843446203</v>
       </c>
-      <c r="F6" s="61">
+      <c r="F6" s="86">
         <v>0.744791852855714</v>
       </c>
-      <c r="G6" s="62">
+      <c r="G6" s="87">
         <v>0.000967226842867905</v>
       </c>
     </row>
@@ -1094,19 +1437,19 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="C7" s="63">
+      <c r="C7" s="88">
         <v>272</v>
       </c>
-      <c r="D7" s="59">
+      <c r="D7" s="84">
         <v>0.136338371062558</v>
       </c>
-      <c r="E7" s="60">
+      <c r="E7" s="85">
         <v>0.111841445233229</v>
       </c>
-      <c r="F7" s="61">
+      <c r="F7" s="86">
         <v>0.751820183704213</v>
       </c>
-      <c r="G7" s="62">
+      <c r="G7" s="87">
         <v>0</v>
       </c>
     </row>
@@ -1121,19 +1464,19 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="C8" s="63">
+      <c r="C8" s="88">
         <v>240</v>
       </c>
-      <c r="D8" s="59">
+      <c r="D8" s="84">
         <v>0.209618412700499</v>
       </c>
-      <c r="E8" s="60">
+      <c r="E8" s="85">
         <v>0.131500879779058</v>
       </c>
-      <c r="F8" s="61">
+      <c r="F8" s="86">
         <v>0.651516195074017</v>
       </c>
-      <c r="G8" s="62">
+      <c r="G8" s="87">
         <v>0.00736451244642682</v>
       </c>
     </row>
@@ -1148,19 +1491,19 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="C9" s="63">
+      <c r="C9" s="88">
         <v>249</v>
       </c>
-      <c r="D9" s="59">
+      <c r="D9" s="84">
         <v>0.181301163183468</v>
       </c>
-      <c r="E9" s="60">
+      <c r="E9" s="85">
         <v>0.117584831864874</v>
       </c>
-      <c r="F9" s="61">
+      <c r="F9" s="86">
         <v>0.69399686143753</v>
       </c>
-      <c r="G9" s="62">
+      <c r="G9" s="87">
         <v>0.00711714351412855</v>
       </c>
     </row>
@@ -1176,41 +1519,41 @@
   <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="34.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="90" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="90" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="90" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="90" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="90" t="inlineStr">
         <is>
           <t>Índice de Riesgo de Victimización</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="90" t="inlineStr">
         <is>
           <t>Categoría de riesgo</t>
         </is>
@@ -1235,7 +1578,7 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E2" s="64">
+      <c r="E2" s="91">
         <v>0.16176668</v>
       </c>
       <c r="F2" t="inlineStr">
@@ -1263,7 +1606,7 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E3" s="64">
+      <c r="E3" s="91">
         <v>0.13918458</v>
       </c>
       <c r="F3" t="inlineStr">
@@ -1291,7 +1634,7 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E4" s="64">
+      <c r="E4" s="91">
         <v>0.11724603</v>
       </c>
       <c r="F4" t="inlineStr">
@@ -1319,7 +1662,7 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E5" s="64">
+      <c r="E5" s="91">
         <v>0.16134331</v>
       </c>
       <c r="F5" t="inlineStr">
@@ -1347,7 +1690,7 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E6" s="64">
+      <c r="E6" s="91">
         <v>0.18139066</v>
       </c>
       <c r="F6" t="inlineStr">
@@ -1368,41 +1711,41 @@
   <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="34.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="93" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="93" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="93" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="93" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="93" t="inlineStr">
         <is>
           <t>Personas dadas por desaparecidas</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="93" t="inlineStr">
         <is>
           <t>Proporción dentro de la provincia</t>
         </is>
@@ -1427,10 +1770,10 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E2" s="65">
+      <c r="E2" s="95">
         <v>61</v>
       </c>
-      <c r="F2" s="67">
+      <c r="F2" s="97">
         <v>0.414965986394558</v>
       </c>
     </row>
@@ -1453,10 +1796,10 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E3" s="65">
+      <c r="E3" s="95">
         <v>41</v>
       </c>
-      <c r="F3" s="67">
+      <c r="F3" s="97">
         <v>0.27891156462585</v>
       </c>
     </row>
@@ -1479,10 +1822,10 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E4" s="65">
+      <c r="E4" s="95">
         <v>21</v>
       </c>
-      <c r="F4" s="67">
+      <c r="F4" s="97">
         <v>0.142857142857143</v>
       </c>
     </row>
@@ -1505,10 +1848,10 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E5" s="65">
+      <c r="E5" s="95">
         <v>19</v>
       </c>
-      <c r="F5" s="67">
+      <c r="F5" s="97">
         <v>0.129251700680272</v>
       </c>
     </row>
@@ -1531,38 +1874,38 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E6" s="65">
+      <c r="E6" s="95">
         <v>5</v>
       </c>
-      <c r="F6" s="67">
+      <c r="F6" s="97">
         <v>0.0340136054421769</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="94" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="94" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="94" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="94" t="inlineStr">
         <is>
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E7" s="66">
+      <c r="E7" s="96">
         <v>147</v>
       </c>
-      <c r="F7" s="68">
+      <c r="F7" s="98">
         <v>1</v>
       </c>
     </row>
@@ -1575,299 +1918,239 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="6.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="44.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="63.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="62.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>periodo</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>ambito</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>valor</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>n_resp</t>
+      <c r="A1" s="100" t="inlineStr">
+        <is>
+          <t>Código DANE</t>
+        </is>
+      </c>
+      <c r="B1" s="100" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C1" s="100" t="inlineStr">
+        <is>
+          <t>Subregión</t>
+        </is>
+      </c>
+      <c r="D1" s="100" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="E1" s="100" t="inlineStr">
+        <is>
+          <t>Sujetos de reparación colectiva reconocidos</t>
+        </is>
+      </c>
+      <c r="F1" s="100" t="inlineStr">
+        <is>
+          <t>Sujetos con Plan Integral de Reparación Colectiva implementado</t>
+        </is>
+      </c>
+      <c r="G1" s="100" t="inlineStr">
+        <is>
+          <t>% de avance del PIRC, promedio (solo sujetos con plan activo)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2">
-        <v>2018</v>
+        <v>5086</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>En su barrio o vereda</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>0.247309549143037</v>
-      </c>
-      <c r="D2">
-        <v>344</v>
+          <t>Belmira</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PROVINCIA DEL RIO GRANDE</t>
+        </is>
+      </c>
+      <c r="E2" s="102">
+        <v>0</v>
+      </c>
+      <c r="F2" s="104">
+        <v>0</v>
+      </c>
+      <c r="G2" s="106" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2019 (1)</t>
-        </is>
+      <c r="A3">
+        <v>5237</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>En su barrio o vereda</t>
-        </is>
-      </c>
-      <c r="C3">
-        <v>0.181036257130808</v>
-      </c>
-      <c r="D3">
-        <v>344</v>
+          <t>Donmatías</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>PROVINCIA DEL RIO GRANDE</t>
+        </is>
+      </c>
+      <c r="E3" s="102">
+        <v>0</v>
+      </c>
+      <c r="F3" s="104">
+        <v>0</v>
+      </c>
+      <c r="G3" s="106" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2019 (2)</t>
-        </is>
+      <c r="A4">
+        <v>5264</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>En su barrio o vereda</t>
-        </is>
-      </c>
-      <c r="C4">
-        <v>0.145889472818591</v>
-      </c>
-      <c r="D4">
-        <v>336</v>
+          <t>Entrerríos</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PROVINCIA DEL RIO GRANDE</t>
+        </is>
+      </c>
+      <c r="E4" s="102">
+        <v>0</v>
+      </c>
+      <c r="F4" s="104">
+        <v>0</v>
+      </c>
+      <c r="G4" s="106" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>2021</v>
+        <v>5664</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>En su barrio o vereda</t>
-        </is>
-      </c>
-      <c r="C5">
-        <v>0.186356719168937</v>
-      </c>
-      <c r="D5">
-        <v>216</v>
+          <t>San Pedro de los Milagros</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PROVINCIA DEL RIO GRANDE</t>
+        </is>
+      </c>
+      <c r="E5" s="102">
+        <v>0</v>
+      </c>
+      <c r="F5" s="104">
+        <v>0</v>
+      </c>
+      <c r="G5" s="106" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>2022</v>
+        <v>5686</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>En su barrio o vereda</t>
-        </is>
-      </c>
-      <c r="C6">
-        <v>0.148855733765853</v>
-      </c>
-      <c r="D6">
-        <v>272</v>
+          <t>Santa Rosa de Osos</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PROVINCIA DEL RIO GRANDE</t>
+        </is>
+      </c>
+      <c r="E6" s="102">
+        <v>0</v>
+      </c>
+      <c r="F6" s="104">
+        <v>0</v>
+      </c>
+      <c r="G6" s="106" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>2023</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>En su barrio o vereda</t>
-        </is>
-      </c>
-      <c r="C7">
-        <v>0.157717210185655</v>
-      </c>
-      <c r="D7">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8">
-        <v>2024</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>En su barrio o vereda</t>
-        </is>
-      </c>
-      <c r="C8">
-        <v>0.155654086292368</v>
-      </c>
-      <c r="D8">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9">
-        <v>2025</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>En su barrio o vereda</t>
-        </is>
-      </c>
-      <c r="C9">
-        <v>0.10353955335921</v>
-      </c>
-      <c r="D9">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10">
-        <v>2018</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>En su municipio</t>
-        </is>
-      </c>
-      <c r="C10">
-        <v>0.36013503474462</v>
-      </c>
-      <c r="D10">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2019 (1)</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>En su municipio</t>
-        </is>
-      </c>
-      <c r="C11">
-        <v>0.251598090378401</v>
-      </c>
-      <c r="D11">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2019 (2)</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>En su municipio</t>
-        </is>
-      </c>
-      <c r="C12">
-        <v>0.208759158077822</v>
-      </c>
-      <c r="D12">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13">
-        <v>2021</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>En su municipio</t>
-        </is>
-      </c>
-      <c r="C13">
-        <v>0.253178411584232</v>
-      </c>
-      <c r="D13">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14">
-        <v>2022</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>En su municipio</t>
-        </is>
-      </c>
-      <c r="C14">
-        <v>0.160979631898894</v>
-      </c>
-      <c r="D14">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15">
-        <v>2023</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>En su municipio</t>
-        </is>
-      </c>
-      <c r="C15">
-        <v>0.230572694316667</v>
-      </c>
-      <c r="D15">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16">
-        <v>2024</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>En su municipio</t>
-        </is>
-      </c>
-      <c r="C16">
-        <v>0.239238869999379</v>
-      </c>
-      <c r="D16">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17">
-        <v>2025</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>En su municipio</t>
-        </is>
-      </c>
-      <c r="C17">
-        <v>0.208948079783054</v>
-      </c>
-      <c r="D17">
-        <v>249</v>
+      <c r="A7" s="101" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B7" s="101" t="inlineStr">
+        <is>
+          <t>TOTAL PROVINCIA DEL RÍO GRANDE</t>
+        </is>
+      </c>
+      <c r="C7" s="101" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D7" s="101" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E7" s="103">
+        <v>0</v>
+      </c>
+      <c r="F7" s="105">
+        <v>0</v>
+      </c>
+      <c r="G7" s="107" t="e">
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
@@ -1879,116 +2162,73 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="4" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
+    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>municipio</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>n_solicitudes</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>pob</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>tasa_solicitudes</t>
+      <c r="A1" s="109" t="inlineStr">
+        <is>
+          <t>Código DANE</t>
+        </is>
+      </c>
+      <c r="B1" s="109" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C1" s="109" t="inlineStr">
+        <is>
+          <t>Subregión</t>
+        </is>
+      </c>
+      <c r="D1" s="109" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="E1" s="109" t="inlineStr">
+        <is>
+          <t>Sujeto de reparación colectiva</t>
+        </is>
+      </c>
+      <c r="F1" s="109" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="G1" s="109" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="H1" s="109" t="inlineStr">
+        <is>
+          <t>Fase del Plan Integral de Reparación Colectiva</t>
+        </is>
+      </c>
+      <c r="I1" s="110" t="inlineStr">
+        <is>
+          <t>% de avance del PIRC</t>
+        </is>
+      </c>
+      <c r="J1" s="109" t="inlineStr">
+        <is>
+          <t>Zona PDET</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Belmira</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>11</v>
-      </c>
-      <c r="C2">
-        <v>6151</v>
-      </c>
-      <c r="D2">
-        <v>1.78832710128434</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Donmatías</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>9</v>
-      </c>
-      <c r="C3">
-        <v>19793</v>
-      </c>
-      <c r="D3">
-        <v>0.454706209265902</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Entrerríos</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>13</v>
-      </c>
-      <c r="C4">
-        <v>12736</v>
-      </c>
-      <c r="D4">
-        <v>1.02072864321608</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>San Pedro de los Milagros</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>12</v>
-      </c>
-      <c r="C5">
-        <v>22287</v>
-      </c>
-      <c r="D5">
-        <v>0.538430475164894</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Santa Rosa de Osos</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>32</v>
-      </c>
-      <c r="C6">
-        <v>40261</v>
-      </c>
-      <c r="D6">
-        <v>0.794813839695984</v>
-      </c>
+      <c r="I2" s="111"/>
     </row>
   </sheetData>
   <printOptions gridLines="1" gridLinesSet="1"/>
@@ -1999,94 +2239,299 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="7.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>municipio</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>desaparecidos</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>prop_desaparecidos</t>
+      <c r="A1" s="113" t="inlineStr">
+        <is>
+          <t>periodo</t>
+        </is>
+      </c>
+      <c r="B1" s="113" t="inlineStr">
+        <is>
+          <t>ambito</t>
+        </is>
+      </c>
+      <c r="C1" s="113" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+      <c r="D1" s="113" t="inlineStr">
+        <is>
+          <t>n_resp</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Santa Rosa de Osos</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>61</v>
+      <c r="A2">
+        <v>2018</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>En su barrio o vereda</t>
+        </is>
       </c>
       <c r="C2">
-        <v>0.414965986394558</v>
+        <v>0.247309549143037</v>
+      </c>
+      <c r="D2">
+        <v>344</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>San Pedro de los Milagros</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>41</v>
+          <t>2019 (1)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>En su barrio o vereda</t>
+        </is>
       </c>
       <c r="C3">
-        <v>0.27891156462585</v>
+        <v>0.181036257130808</v>
+      </c>
+      <c r="D3">
+        <v>344</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Donmatías</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>21</v>
+          <t>2019 (2)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>En su barrio o vereda</t>
+        </is>
       </c>
       <c r="C4">
-        <v>0.142857142857143</v>
+        <v>0.145889472818591</v>
+      </c>
+      <c r="D4">
+        <v>336</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Belmira</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>19</v>
+      <c r="A5">
+        <v>2021</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>En su barrio o vereda</t>
+        </is>
       </c>
       <c r="C5">
-        <v>0.129251700680272</v>
+        <v>0.186356719168937</v>
+      </c>
+      <c r="D5">
+        <v>216</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Entrerríos</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>5</v>
+      <c r="A6">
+        <v>2022</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>En su barrio o vereda</t>
+        </is>
       </c>
       <c r="C6">
-        <v>0.0340136054421769</v>
+        <v>0.148855733765853</v>
+      </c>
+      <c r="D6">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>2023</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>En su barrio o vereda</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>0.157717210185655</v>
+      </c>
+      <c r="D7">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>2024</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>En su barrio o vereda</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>0.155654086292368</v>
+      </c>
+      <c r="D8">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>2025</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>En su barrio o vereda</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>0.10353955335921</v>
+      </c>
+      <c r="D9">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>2018</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>En su municipio</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>0.36013503474462</v>
+      </c>
+      <c r="D10">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2019 (1)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>En su municipio</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>0.251598090378401</v>
+      </c>
+      <c r="D11">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2019 (2)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>En su municipio</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>0.208759158077822</v>
+      </c>
+      <c r="D12">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>2021</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>En su municipio</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>0.253178411584232</v>
+      </c>
+      <c r="D13">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>2022</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>En su municipio</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>0.160979631898894</v>
+      </c>
+      <c r="D14">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>2023</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>En su municipio</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>0.230572694316667</v>
+      </c>
+      <c r="D15">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>2024</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>En su municipio</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>0.239238869999379</v>
+      </c>
+      <c r="D16">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>2025</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>En su municipio</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>0.208948079783054</v>
+      </c>
+      <c r="D17">
+        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -2098,22 +2543,34 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="6.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="115" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>victimas_ocurrencia</t>
+      <c r="B1" s="115" t="inlineStr">
+        <is>
+          <t>n_solicitudes</t>
+        </is>
+      </c>
+      <c r="C1" s="115" t="inlineStr">
+        <is>
+          <t>pob</t>
+        </is>
+      </c>
+      <c r="D1" s="115" t="inlineStr">
+        <is>
+          <t>tasa_solicitudes</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2581,13 @@
         </is>
       </c>
       <c r="B2">
-        <v>1275</v>
+        <v>11</v>
+      </c>
+      <c r="C2">
+        <v>6151</v>
+      </c>
+      <c r="D2">
+        <v>1.78832710128434</v>
       </c>
     </row>
     <row r="3">
@@ -2134,7 +2597,13 @@
         </is>
       </c>
       <c r="B3">
-        <v>1499</v>
+        <v>9</v>
+      </c>
+      <c r="C3">
+        <v>19793</v>
+      </c>
+      <c r="D3">
+        <v>0.454706209265902</v>
       </c>
     </row>
     <row r="4">
@@ -2144,7 +2613,13 @@
         </is>
       </c>
       <c r="B4">
-        <v>551</v>
+        <v>13</v>
+      </c>
+      <c r="C4">
+        <v>12736</v>
+      </c>
+      <c r="D4">
+        <v>1.02072864321608</v>
       </c>
     </row>
     <row r="5">
@@ -2154,7 +2629,13 @@
         </is>
       </c>
       <c r="B5">
-        <v>9848</v>
+        <v>12</v>
+      </c>
+      <c r="C5">
+        <v>22287</v>
+      </c>
+      <c r="D5">
+        <v>0.538430475164894</v>
       </c>
     </row>
     <row r="6">
@@ -2164,7 +2645,13 @@
         </is>
       </c>
       <c r="B6">
-        <v>5031</v>
+        <v>32</v>
+      </c>
+      <c r="C6">
+        <v>40261</v>
+      </c>
+      <c r="D6">
+        <v>0.794813839695984</v>
       </c>
     </row>
   </sheetData>
@@ -2176,237 +2663,94 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>hecho</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>victimas_ocurrencia</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>proporcion_pct</t>
+      <c r="A1" s="117" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="117" t="inlineStr">
+        <is>
+          <t>desaparecidos</t>
+        </is>
+      </c>
+      <c r="C1" s="117" t="inlineStr">
+        <is>
+          <t>prop_desaparecidos</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Desplazamiento forzado</t>
+          <t>Santa Rosa de Osos</t>
         </is>
       </c>
       <c r="B2">
-        <v>13134</v>
+        <v>61</v>
       </c>
       <c r="C2">
-        <v>0.721489782465392</v>
+        <v>0.414965986394558</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Homicidio</t>
+          <t>San Pedro de los Milagros</t>
         </is>
       </c>
       <c r="B3">
-        <v>3303</v>
+        <v>41</v>
       </c>
       <c r="C3">
-        <v>0.181443638760712</v>
+        <v>0.27891156462585</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Amenaza</t>
+          <t>Donmatías</t>
         </is>
       </c>
       <c r="B4">
-        <v>1118</v>
+        <v>21</v>
       </c>
       <c r="C4">
-        <v>0.0614150736101956</v>
+        <v>0.142857142857143</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Desaparición forzada</t>
+          <t>Belmira</t>
         </is>
       </c>
       <c r="B5">
-        <v>332</v>
+        <v>19</v>
       </c>
       <c r="C5">
-        <v>0.018237749945067</v>
+        <v>0.129251700680272</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Secuestro</t>
+          <t>Entrerríos</t>
         </is>
       </c>
       <c r="B6">
-        <v>90</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>0.00494396835860251</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Pérdida de bienes muebles/inmuebles</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>53</v>
-      </c>
-      <c r="C7">
-        <v>0.00291144803339925</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Acto terrorista/atentados/combates</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>49</v>
-      </c>
-      <c r="C8">
-        <v>0.00269171610635025</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Delitos contra libertad/integridad sexual</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>44</v>
-      </c>
-      <c r="C9">
-        <v>0.002417051197539</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Lesiones personales psicológicas</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>24</v>
-      </c>
-      <c r="C10">
-        <v>0.001318391562294</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Tortura</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>20</v>
-      </c>
-      <c r="C11">
-        <v>0.001098659635245</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Lesiones personales físicas</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>15</v>
-      </c>
-      <c r="C12">
-        <v>0.000823994726433751</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Abandono o despojo de tierras</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>11</v>
-      </c>
-      <c r="C13">
-        <v>0.000604262799384751</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Vinculación de NNA a grupos armados</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>9</v>
-      </c>
-      <c r="C14">
-        <v>0.000494396835860251</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Minas antipersonal/MUSE</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>2</v>
-      </c>
-      <c r="C15">
-        <v>0.0001098659635245</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Confinamiento</t>
-        </is>
-      </c>
-      <c r="B16">
-        <v>0</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Sin información</t>
-        </is>
-      </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
+        <v>0.0340136054421769</v>
       </c>
     </row>
   </sheetData>
@@ -2418,94 +2762,73 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Código DANE</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Municipio</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Homicidios por 100.000 hab.</t>
+      <c r="A1" s="119" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="119" t="inlineStr">
+        <is>
+          <t>victimas_ocurrencia</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>5086</v>
-      </c>
-      <c r="B2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Belmira</t>
         </is>
       </c>
-      <c r="C2">
-        <v>81.2875955129247</v>
+      <c r="B2">
+        <v>1275</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>5237</v>
-      </c>
-      <c r="B3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Donmatías</t>
         </is>
       </c>
-      <c r="C3">
-        <v>25.2614560703279</v>
+      <c r="B3">
+        <v>1499</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>5264</v>
-      </c>
-      <c r="B4" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Entrerríos</t>
         </is>
       </c>
-      <c r="C4">
-        <v>15.7035175879397</v>
+      <c r="B4">
+        <v>551</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>5664</v>
-      </c>
-      <c r="B5" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>San Pedro de los Milagros</t>
         </is>
       </c>
-      <c r="C5">
-        <v>31.4084443846188</v>
+      <c r="B5">
+        <v>9848</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5686</v>
-      </c>
-      <c r="B6" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Santa Rosa de Osos</t>
         </is>
       </c>
-      <c r="C6">
-        <v>22.3541392414495</v>
+      <c r="B6">
+        <v>5031</v>
       </c>
     </row>
   </sheetData>
@@ -2520,394 +2843,394 @@
   <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>Año</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="8" t="inlineStr">
         <is>
           <t>Hectáreas con permisos</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="8" t="inlineStr">
         <is>
           <t>Hectáreas en tránsito</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="8" t="inlineStr">
         <is>
           <t>Hectáreas ilícita</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="8" t="inlineStr">
         <is>
           <t>Total EVOA (ha)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="9" t="inlineStr">
         <is>
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="10">
         <v>2018</v>
       </c>
-      <c r="F2" s="8">
+      <c r="F2" s="11">
         <v>0</v>
       </c>
-      <c r="G2" s="9">
+      <c r="G2" s="12">
         <v>0</v>
       </c>
-      <c r="H2" s="10">
+      <c r="H2" s="13">
         <v>0</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="10">
         <v>2019</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F3" s="11">
         <v>0</v>
       </c>
-      <c r="G3" s="9">
+      <c r="G3" s="12">
         <v>0</v>
       </c>
-      <c r="H3" s="10">
+      <c r="H3" s="13">
         <v>0</v>
       </c>
-      <c r="I3" s="11">
+      <c r="I3" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="10">
         <v>2020</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="11">
         <v>0</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4" s="12">
         <v>0</v>
       </c>
-      <c r="H4" s="10">
+      <c r="H4" s="13">
         <v>0</v>
       </c>
-      <c r="I4" s="11">
+      <c r="I4" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>TOTAL SUBREGIÓN NORTE</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>NORTE</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="10">
         <v>2018</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="11">
         <v>0</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="12">
         <v>65.569309</v>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="13">
         <v>480.648761</v>
       </c>
-      <c r="I5" s="11">
+      <c r="I5" s="14">
         <v>546.21807</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>TOTAL SUBREGIÓN NORTE</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>NORTE</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="10">
         <v>2019</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="11">
         <v>0</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="12">
         <v>0.459309</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="13">
         <v>501.344919</v>
       </c>
-      <c r="I6" s="11">
+      <c r="I6" s="14">
         <v>501.804228</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>TOTAL SUBREGIÓN NORTE</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>NORTE</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="10">
         <v>2020</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="11">
         <v>0</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="12">
         <v>129.510881</v>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="13">
         <v>296.684515</v>
       </c>
-      <c r="I7" s="11">
+      <c r="I7" s="14">
         <v>426.195396</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>TOTAL DEPARTAMENTO (ANTIOQUIA)</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>DEPARTAMENTO DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="10">
         <v>2018</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="11">
         <v>16186.547037</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="12">
         <v>1633.054856</v>
       </c>
-      <c r="H8" s="10">
+      <c r="H8" s="13">
         <v>18627.422655</v>
       </c>
-      <c r="I8" s="11">
+      <c r="I8" s="14">
         <v>36447.024548</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>TOTAL DEPARTAMENTO (ANTIOQUIA)</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>DEPARTAMENTO DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="10">
         <v>2019</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="11">
         <v>17799.238713</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="12">
         <v>1658.203768</v>
       </c>
-      <c r="H9" s="10">
+      <c r="H9" s="13">
         <v>20744.042756</v>
       </c>
-      <c r="I9" s="11">
+      <c r="I9" s="14">
         <v>40201.485237</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>TOTAL DEPARTAMENTO (ANTIOQUIA)</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>DEPARTAMENTO DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="10">
         <v>2020</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="11">
         <v>19240.998973</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G10" s="12">
         <v>1806.249069</v>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="13">
         <v>19842.333019</v>
       </c>
-      <c r="I10" s="11">
+      <c r="I10" s="14">
         <v>40889.581061</v>
       </c>
     </row>
@@ -2920,26 +3243,268 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="42.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="121" t="inlineStr">
+        <is>
+          <t>hecho</t>
+        </is>
+      </c>
+      <c r="B1" s="121" t="inlineStr">
+        <is>
+          <t>victimas_ocurrencia</t>
+        </is>
+      </c>
+      <c r="C1" s="121" t="inlineStr">
+        <is>
+          <t>proporcion_pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Desplazamiento forzado</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>13134</v>
+      </c>
+      <c r="C2">
+        <v>0.721489782465392</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Homicidio</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>3303</v>
+      </c>
+      <c r="C3">
+        <v>0.181443638760712</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Amenaza</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>1118</v>
+      </c>
+      <c r="C4">
+        <v>0.0614150736101956</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Desaparición forzada</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>332</v>
+      </c>
+      <c r="C5">
+        <v>0.018237749945067</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Secuestro</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>90</v>
+      </c>
+      <c r="C6">
+        <v>0.00494396835860251</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Pérdida de bienes muebles/inmuebles</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>53</v>
+      </c>
+      <c r="C7">
+        <v>0.00291144803339925</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Acto terrorista/atentados/combates</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>49</v>
+      </c>
+      <c r="C8">
+        <v>0.00269171610635025</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Delitos contra libertad/integridad sexual</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>44</v>
+      </c>
+      <c r="C9">
+        <v>0.002417051197539</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Lesiones personales psicológicas</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>24</v>
+      </c>
+      <c r="C10">
+        <v>0.001318391562294</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Tortura</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>20</v>
+      </c>
+      <c r="C11">
+        <v>0.001098659635245</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Lesiones personales físicas</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>15</v>
+      </c>
+      <c r="C12">
+        <v>0.000823994726433751</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Abandono o despojo de tierras</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>11</v>
+      </c>
+      <c r="C13">
+        <v>0.000604262799384751</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Vinculación de NNA a grupos armados</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>9</v>
+      </c>
+      <c r="C14">
+        <v>0.000494396835860251</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Minas antipersonal/MUSE</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15">
+        <v>0.0001098659635245</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Confinamiento</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Sin información</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="28.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="123" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="123" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="123" t="inlineStr">
         <is>
           <t>Homicidios por 100.000 hab.</t>
         </is>
@@ -2947,314 +3512,1271 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>5004</v>
+        <v>5086</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Abriaquí</t>
+          <t>Belmira</t>
         </is>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>81.2875955129247</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>5138</v>
+        <v>5237</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cañasgordas</t>
+          <t>Donmatías</t>
         </is>
       </c>
       <c r="C3">
-        <v>38.7847446670976</v>
+        <v>25.2614560703279</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>5234</v>
+        <v>5264</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dabeiba</t>
+          <t>Entrerríos</t>
         </is>
       </c>
       <c r="C4">
-        <v>52.4024508223154</v>
+        <v>15.7035175879397</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>5284</v>
+        <v>5664</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Frontino</t>
+          <t>San Pedro de los Milagros</t>
         </is>
       </c>
       <c r="C5">
-        <v>32.1425291578657</v>
+        <v>31.4084443846188</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>5543</v>
+        <v>5686</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Peque</t>
+          <t>Santa Rosa de Osos</t>
         </is>
       </c>
       <c r="C6">
-        <v>11.3869278068777</v>
+        <v>22.3541392414495</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:C91"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="28.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="125" t="inlineStr">
+        <is>
+          <t>Código DANE</t>
+        </is>
+      </c>
+      <c r="B1" s="125" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C1" s="125" t="inlineStr">
+        <is>
+          <t>Homicidios por 100.000 hab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>5001</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>13.1706813513831</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>5002</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Abejorral</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>28.3728188395517</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>5004</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Abriaquí</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>5021</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Alejandría</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>18.9214758751183</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>5030</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Amagá</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>36.5207864142675</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>5842</v>
+        <v>5031</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Uramita</t>
+          <t>Amalfi</t>
         </is>
       </c>
       <c r="C7">
-        <v>13.4138162307176</v>
+        <v>113.581606663454</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>5038</v>
+        <v>5034</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Angostura</t>
+          <t>Andes</t>
         </is>
       </c>
       <c r="C8">
-        <v>55.9507633282711</v>
+        <v>147.684440231887</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>5040</v>
+        <v>5036</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Anorí</t>
+          <t>Angelópolis</t>
         </is>
       </c>
       <c r="C9">
-        <v>218.683147135726</v>
+        <v>48.363694986297</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>5107</v>
+        <v>5038</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Briceño</t>
+          <t>Angostura</t>
         </is>
       </c>
       <c r="C10">
-        <v>226.21591051904</v>
+        <v>55.9507633282711</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>5134</v>
+        <v>5040</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Campamento</t>
+          <t>Anorí</t>
         </is>
       </c>
       <c r="C11">
-        <v>99.9500249875062</v>
+        <v>218.683147135726</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>5150</v>
+        <v>5042</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Carolina del Príncipe</t>
+          <t>Santa Fe de Antioquia</t>
         </is>
       </c>
       <c r="C12">
-        <v>76.103500761035</v>
+        <v>31.6667253087506</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>5315</v>
+        <v>5044</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Guadalupe</t>
+          <t>Anzá</t>
         </is>
       </c>
       <c r="C13">
-        <v>42.8021115708375</v>
+        <v>52.0765525322224</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>5310</v>
+        <v>5055</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Gómez Plata</t>
+          <t>Argelia</t>
         </is>
       </c>
       <c r="C14">
-        <v>57.8424756579582</v>
+        <v>12.1728545343883</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>5361</v>
+        <v>5079</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ituango</t>
+          <t>Barbosa</t>
         </is>
       </c>
       <c r="C15">
-        <v>71.15026257835</v>
+        <v>17.3351193759357</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>5647</v>
+        <v>5086</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>San Andrés de Cuerquía</t>
+          <t>Belmira</t>
         </is>
       </c>
       <c r="C16">
-        <v>391.786003782761</v>
+        <v>81.2875955129247</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>5658</v>
+        <v>5088</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>San José de la Montaña</t>
+          <t>Bello</t>
         </is>
       </c>
       <c r="C17">
-        <v>74.6825989544436</v>
+        <v>7.64226237548096</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>5819</v>
+        <v>5091</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Toledo</t>
+          <t>Betania</t>
         </is>
       </c>
       <c r="C18">
-        <v>124.378109452736</v>
+        <v>176.727746256162</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>5854</v>
+        <v>5093</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Valdivia</t>
+          <t>Betulia</t>
         </is>
       </c>
       <c r="C19">
-        <v>126.548554682297</v>
+        <v>206.124852767962</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>5887</v>
+        <v>5101</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Yarumal</t>
+          <t>Ciudad Bolívar</t>
         </is>
       </c>
       <c r="C20">
-        <v>59.6886639289466</v>
+        <v>137.815979400138</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>5086</v>
+        <v>5107</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Belmira</t>
+          <t>Briceño</t>
         </is>
       </c>
       <c r="C21">
-        <v>81.2875955129247</v>
+        <v>226.21591051904</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>5237</v>
+        <v>5113</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Donmatías</t>
+          <t>Buriticá</t>
         </is>
       </c>
       <c r="C22">
-        <v>25.2614560703279</v>
+        <v>90.7852927825692</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>5264</v>
+        <v>5125</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Entrerríos</t>
+          <t>Caicedo</t>
         </is>
       </c>
       <c r="C23">
-        <v>15.7035175879397</v>
+        <v>32.9416932030306</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>5664</v>
+        <v>5129</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>San Pedro de los Milagros</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="C24">
-        <v>31.4084443846188</v>
+        <v>12.3495599065924</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
+        <v>5134</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Campamento</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>99.9500249875062</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>5138</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Cañasgordas</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>38.7847446670976</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>5145</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Caramanta</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>22.2271615914648</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>5150</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>76.103500761035</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>5197</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Cocorná</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>24.8617067561688</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>5206</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Concepción</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>39.1236306729264</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>5209</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Concordia</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>99.2645399990976</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>5212</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Copacabana</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>16.5049184657028</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>5234</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Dabeiba</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>52.4024508223154</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>5237</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Donmatías</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>25.2614560703279</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>5240</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Ebéjico</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>5264</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Entrerríos</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>15.7035175879397</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>5266</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>3.02300887630981</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>5282</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Fredonia</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>22.7264118783379</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>5284</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Frontino</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>32.1425291578657</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>5306</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Giraldo</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>15.6152404747033</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>5308</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Girardota</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>4.88289197415322</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>5310</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>57.8424756579582</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>5313</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>19.0276852820854</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>5315</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>42.8021115708375</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>5321</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Guatapé</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>30.9437854564208</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>5347</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Heliconia</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>39.6982929734021</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>5353</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Hispania</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>168.662506324844</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>5360</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Itagüí</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>3.61215918457148</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>5361</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>71.15026257835</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>5364</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Jardín</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>71.2758374910905</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>5368</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Jericó</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>69.5603784084585</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>5380</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>La Estrella</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>9.62822997027284</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>5390</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>La Pintada</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>80.887450889762</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>5400</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>70.6655027642682</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>5440</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Marinilla</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>33.6066675628445</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>5467</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Montebello</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>45.8855919241358</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>5483</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>63.6363636363636</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>5501</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Olaya</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>5541</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Peñol</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>41.9691946111554</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>5543</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Peque</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>11.3869278068777</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>5576</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Pueblorrico</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>99.41455870982</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>5604</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Remedios</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>118.106659398565</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>5628</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>80.7346856393178</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>5631</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Sabaneta</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>2.81288677193114</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>5642</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Salgar</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>100.396301188904</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>5647</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>391.786003782761</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>5649</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>11.8077695123391</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>5652</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>33.0141961043249</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>5656</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>San Jerónimo</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>81.7661488143908</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>5658</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>74.6825989544436</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>5660</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>San Luis</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>62.2966705890496</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>5664</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>San Pedro de los Milagros</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>31.4084443846188</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>5667</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>San Rafael</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>22.9739819654242</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>5674</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>San Vicente Ferrer</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>40.3616402970617</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>5679</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Santa Bárbara</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>33.9328130302002</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
         <v>5686</v>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>Santa Rosa de Osos</t>
         </is>
       </c>
-      <c r="C25">
+      <c r="C76">
         <v>22.3541392414495</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>5736</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>66.0854535749689</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>5756</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Sonsón</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>38.9105058365759</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>5789</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Támesis</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>5.99736116108912</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>5792</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Tarso</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>76.2660158633313</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>5809</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Titiribí</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>60.6743520845974</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>5819</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>124.378109452736</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>5842</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Uramita</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>13.4138162307176</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>5847</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Urrao</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>96.9113417531574</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>5854</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>126.548554682297</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>5856</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>14.8942508191838</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>5858</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Vegachí</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>41.1184210526316</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>5861</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Venecia</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>40.2835965194973</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>5885</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Yalí</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>25.9100919808265</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>5887</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>59.6886639289466</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>5890</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Yolombó</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>31.9514338205927</v>
       </c>
     </row>
   </sheetData>
@@ -3269,47 +4791,47 @@
   <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="28.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="34.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="16" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="16" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="16" t="inlineStr">
         <is>
           <t>Hurtos por 100.000 hab.</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="16" t="inlineStr">
         <is>
           <t>Homicidios por 100.000 hab.</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="16" t="inlineStr">
         <is>
           <t>Violencia intrafamiliar por 100.000 hab.</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="16" t="inlineStr">
         <is>
           <t>Delitos sexuales por 100.000 hab.</t>
         </is>
@@ -3329,16 +4851,16 @@
           <t>NORTE</t>
         </is>
       </c>
-      <c r="D2" s="12">
+      <c r="D2" s="18">
         <v>48.7725573077548</v>
       </c>
-      <c r="E2" s="14">
+      <c r="E2" s="20">
         <v>81.2875955129247</v>
       </c>
-      <c r="F2" s="16">
+      <c r="F2" s="22">
         <v>81.2875955129247</v>
       </c>
-      <c r="G2" s="18">
+      <c r="G2" s="24">
         <v>81.2875955129247</v>
       </c>
     </row>
@@ -3356,16 +4878,16 @@
           <t>NORTE</t>
         </is>
       </c>
-      <c r="D3" s="12">
+      <c r="D3" s="18">
         <v>151.568736421967</v>
       </c>
-      <c r="E3" s="14">
+      <c r="E3" s="20">
         <v>25.2614560703279</v>
       </c>
-      <c r="F3" s="16">
+      <c r="F3" s="22">
         <v>252.614560703279</v>
       </c>
-      <c r="G3" s="18">
+      <c r="G3" s="24">
         <v>75.7843682109837</v>
       </c>
     </row>
@@ -3383,16 +4905,16 @@
           <t>NORTE</t>
         </is>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="18">
         <v>54.9623115577889</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="20">
         <v>15.7035175879397</v>
       </c>
-      <c r="F4" s="16">
+      <c r="F4" s="22">
         <v>133.479899497487</v>
       </c>
-      <c r="G4" s="18">
+      <c r="G4" s="24">
         <v>86.3693467336684</v>
       </c>
     </row>
@@ -3410,16 +4932,16 @@
           <t>NORTE</t>
         </is>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="18">
         <v>139.094539417598</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="20">
         <v>31.4084443846188</v>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="22">
         <v>148.068380670346</v>
       </c>
-      <c r="G5" s="18">
+      <c r="G5" s="24">
         <v>98.7122537802306</v>
       </c>
     </row>
@@ -3437,103 +4959,103 @@
           <t>NORTE</t>
         </is>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="18">
         <v>136.608628697747</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="20">
         <v>22.3541392414495</v>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="22">
         <v>79.4813839695984</v>
       </c>
-      <c r="G6" s="18">
+      <c r="G6" s="24">
         <v>54.6434514790989</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="19">
         <v>124.471490101553</v>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="21">
         <v>27.6603311336784</v>
       </c>
-      <c r="F7" s="17">
+      <c r="F7" s="23">
         <v>135.338048761212</v>
       </c>
-      <c r="G7" s="19">
+      <c r="G7" s="25">
         <v>74.0901726794958</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>TOTAL SUBREGIÓN NORTE</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>NORTE</t>
-        </is>
-      </c>
-      <c r="D8" s="13">
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="D8" s="19">
         <v>80.5691467101584</v>
       </c>
-      <c r="E8" s="15">
+      <c r="E8" s="21">
         <v>69.6180005553796</v>
       </c>
-      <c r="F8" s="17">
+      <c r="F8" s="23">
         <v>123.591506603932</v>
       </c>
-      <c r="G8" s="19">
+      <c r="G8" s="25">
         <v>75.093573632769</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>TOTAL DEPARTAMENTO (ANTIOQUIA)</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="19">
         <v>506.74242087463</v>
       </c>
-      <c r="E9" s="15">
+      <c r="E9" s="21">
         <v>25.3306260114209</v>
       </c>
-      <c r="F9" s="17">
+      <c r="F9" s="23">
         <v>276.471875355423</v>
       </c>
-      <c r="G9" s="19">
+      <c r="G9" s="25">
         <v>71.9216577862736</v>
       </c>
     </row>
@@ -3549,59 +5071,59 @@
   <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="7.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="27" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="27" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="27" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="27" t="inlineStr">
         <is>
           <t>Víctimas por ocurrencia</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="27" t="inlineStr">
         <is>
           <t>Víctimas por declaración</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="27" t="inlineStr">
         <is>
           <t>Víctimas por ubicación</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="27" t="inlineStr">
         <is>
           <t>Sujetos de atención</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="27" t="inlineStr">
         <is>
           <t>Eventos</t>
         </is>
@@ -3626,19 +5148,19 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E2" s="20">
+      <c r="E2" s="29">
         <v>1275</v>
       </c>
-      <c r="F2" s="22">
+      <c r="F2" s="31">
         <v>640</v>
       </c>
-      <c r="G2" s="24">
+      <c r="G2" s="33">
         <v>674</v>
       </c>
-      <c r="H2" s="26">
+      <c r="H2" s="35">
         <v>581</v>
       </c>
-      <c r="I2" s="28">
+      <c r="I2" s="37">
         <v>1311</v>
       </c>
     </row>
@@ -3661,19 +5183,19 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E3" s="20">
+      <c r="E3" s="29">
         <v>1499</v>
       </c>
-      <c r="F3" s="22">
+      <c r="F3" s="31">
         <v>3256</v>
       </c>
-      <c r="G3" s="24">
+      <c r="G3" s="33">
         <v>3228</v>
       </c>
-      <c r="H3" s="26">
+      <c r="H3" s="35">
         <v>2782</v>
       </c>
-      <c r="I3" s="28">
+      <c r="I3" s="37">
         <v>1520</v>
       </c>
     </row>
@@ -3696,19 +5218,19 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E4" s="20">
+      <c r="E4" s="29">
         <v>551</v>
       </c>
-      <c r="F4" s="22">
+      <c r="F4" s="31">
         <v>514</v>
       </c>
-      <c r="G4" s="24">
+      <c r="G4" s="33">
         <v>979</v>
       </c>
-      <c r="H4" s="26">
+      <c r="H4" s="35">
         <v>845</v>
       </c>
-      <c r="I4" s="28">
+      <c r="I4" s="37">
         <v>559</v>
       </c>
     </row>
@@ -3731,19 +5253,19 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="29">
         <v>9848</v>
       </c>
-      <c r="F5" s="22">
+      <c r="F5" s="31">
         <v>2585</v>
       </c>
-      <c r="G5" s="24">
+      <c r="G5" s="33">
         <v>2875</v>
       </c>
-      <c r="H5" s="26">
+      <c r="H5" s="35">
         <v>2548</v>
       </c>
-      <c r="I5" s="28">
+      <c r="I5" s="37">
         <v>9946</v>
       </c>
     </row>
@@ -3766,56 +5288,56 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="29">
         <v>5031</v>
       </c>
-      <c r="F6" s="22">
+      <c r="F6" s="31">
         <v>3299</v>
       </c>
-      <c r="G6" s="24">
+      <c r="G6" s="33">
         <v>4776</v>
       </c>
-      <c r="H6" s="26">
+      <c r="H6" s="35">
         <v>3974</v>
       </c>
-      <c r="I6" s="28">
+      <c r="I6" s="37">
         <v>5237</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="28" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="28" t="inlineStr">
         <is>
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="30">
         <v>18204</v>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="32">
         <v>10294</v>
       </c>
-      <c r="G7" s="25">
+      <c r="G7" s="34">
         <v>12532</v>
       </c>
-      <c r="H7" s="27">
+      <c r="H7" s="36">
         <v>10730</v>
       </c>
-      <c r="I7" s="29">
+      <c r="I7" s="38">
         <v>18573</v>
       </c>
     </row>
@@ -3831,23 +5353,23 @@
   <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="87.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="29.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="88.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="40" t="inlineStr">
         <is>
           <t>Hecho victimizante</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="40" t="inlineStr">
         <is>
           <t>Víctimas por ocurrencia</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="40" t="inlineStr">
         <is>
           <t>Proporción sobre el total (%)</t>
         </is>
@@ -3859,10 +5381,10 @@
           <t>Desplazamiento forzado</t>
         </is>
       </c>
-      <c r="B2" s="30">
+      <c r="B2" s="41">
         <v>13134</v>
       </c>
-      <c r="C2" s="31">
+      <c r="C2" s="42">
         <v>0.721489782465392</v>
       </c>
     </row>
@@ -3872,10 +5394,10 @@
           <t>Homicidio (Conflicto)</t>
         </is>
       </c>
-      <c r="B3" s="30">
+      <c r="B3" s="41">
         <v>3303</v>
       </c>
-      <c r="C3" s="31">
+      <c r="C3" s="42">
         <v>0.181443638760712</v>
       </c>
     </row>
@@ -3885,10 +5407,10 @@
           <t>Amenaza (Conflicto)</t>
         </is>
       </c>
-      <c r="B4" s="30">
+      <c r="B4" s="41">
         <v>1118</v>
       </c>
-      <c r="C4" s="31">
+      <c r="C4" s="42">
         <v>0.0614150736101956</v>
       </c>
     </row>
@@ -3898,10 +5420,10 @@
           <t>Desaparición forzada</t>
         </is>
       </c>
-      <c r="B5" s="30">
+      <c r="B5" s="41">
         <v>332</v>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="42">
         <v>0.018237749945067</v>
       </c>
     </row>
@@ -3911,10 +5433,10 @@
           <t>Secuestro (Conflicto)</t>
         </is>
       </c>
-      <c r="B6" s="30">
+      <c r="B6" s="41">
         <v>90</v>
       </c>
-      <c r="C6" s="31">
+      <c r="C6" s="42">
         <v>0.00494396835860251</v>
       </c>
     </row>
@@ -3924,10 +5446,10 @@
           <t>Perdida de Bienes Muebles o Inmuebles</t>
         </is>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="41">
         <v>53</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="42">
         <v>0.00291144803339925</v>
       </c>
     </row>
@@ -3937,10 +5459,10 @@
           <t>Acto terrorista / Atentados / Combates / Enfrentamientos / Hostigamientos</t>
         </is>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="41">
         <v>49</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="42">
         <v>0.00269171610635025</v>
       </c>
     </row>
@@ -3950,10 +5472,10 @@
           <t>Delitos contra la libertad y la integridad sexual en desarrollo del conflicto armado</t>
         </is>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="41">
         <v>44</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="42">
         <v>0.002417051197539</v>
       </c>
     </row>
@@ -3963,10 +5485,10 @@
           <t>Lesiones Personales Psicologicas</t>
         </is>
       </c>
-      <c r="B10" s="30">
+      <c r="B10" s="41">
         <v>24</v>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="42">
         <v>0.001318391562294</v>
       </c>
     </row>
@@ -3976,10 +5498,10 @@
           <t>Tortura (Conflicto)</t>
         </is>
       </c>
-      <c r="B11" s="30">
+      <c r="B11" s="41">
         <v>20</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="42">
         <v>0.001098659635245</v>
       </c>
     </row>
@@ -3989,10 +5511,10 @@
           <t>Lesiones Personales Fisicas</t>
         </is>
       </c>
-      <c r="B12" s="30">
+      <c r="B12" s="41">
         <v>15</v>
       </c>
-      <c r="C12" s="31">
+      <c r="C12" s="42">
         <v>0.000823994726433751</v>
       </c>
     </row>
@@ -4002,10 +5524,10 @@
           <t>Abandono o Despojo Forzado de Tierras</t>
         </is>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="41">
         <v>11</v>
       </c>
-      <c r="C13" s="31">
+      <c r="C13" s="42">
         <v>0.000604262799384751</v>
       </c>
     </row>
@@ -4015,10 +5537,10 @@
           <t>Vinculación de Niños Niñas y Adolescentes a Actividades Relacionadas con grupos armados</t>
         </is>
       </c>
-      <c r="B14" s="30">
+      <c r="B14" s="41">
         <v>9</v>
       </c>
-      <c r="C14" s="31">
+      <c r="C14" s="42">
         <v>0.000494396835860251</v>
       </c>
     </row>
@@ -4028,10 +5550,10 @@
           <t>Minas Antipersonal, Munición sin Explotar y Artefacto Explosivo improvisado</t>
         </is>
       </c>
-      <c r="B15" s="30">
+      <c r="B15" s="41">
         <v>2</v>
       </c>
-      <c r="C15" s="31">
+      <c r="C15" s="42">
         <v>0.0001098659635245</v>
       </c>
     </row>
@@ -4041,10 +5563,10 @@
           <t>Confinamiento (Conflicto)</t>
         </is>
       </c>
-      <c r="B16" s="30">
+      <c r="B16" s="41">
         <v>0</v>
       </c>
-      <c r="C16" s="31">
+      <c r="C16" s="42">
         <v>0</v>
       </c>
     </row>
@@ -4054,10 +5576,10 @@
           <t>Sin informacion (Conflicto)</t>
         </is>
       </c>
-      <c r="B17" s="30">
+      <c r="B17" s="41">
         <v>0</v>
       </c>
-      <c r="C17" s="31">
+      <c r="C17" s="42">
         <v>0</v>
       </c>
     </row>
@@ -4067,10 +5589,10 @@
           <t>TOTAL PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="B18" s="30">
+      <c r="B18" s="41">
         <v>18204</v>
       </c>
-      <c r="C18" s="31">
+      <c r="C18" s="42">
         <v>1</v>
       </c>
     </row>
@@ -4086,47 +5608,47 @@
   <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="44" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="44" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="44" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="44" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="44" t="inlineStr">
         <is>
           <t>Número de solicitudes</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="44" t="inlineStr">
         <is>
           <t>Número de predios</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="44" t="inlineStr">
         <is>
           <t>Número de titulares</t>
         </is>
@@ -4151,13 +5673,13 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E2" s="32">
+      <c r="E2" s="46">
         <v>11</v>
       </c>
-      <c r="F2" s="34">
+      <c r="F2" s="48">
         <v>9</v>
       </c>
-      <c r="G2" s="36">
+      <c r="G2" s="50">
         <v>9</v>
       </c>
     </row>
@@ -4180,13 +5702,13 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E3" s="32">
+      <c r="E3" s="46">
         <v>9</v>
       </c>
-      <c r="F3" s="34">
+      <c r="F3" s="48">
         <v>9</v>
       </c>
-      <c r="G3" s="36">
+      <c r="G3" s="50">
         <v>7</v>
       </c>
     </row>
@@ -4209,13 +5731,13 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E4" s="32">
+      <c r="E4" s="46">
         <v>13</v>
       </c>
-      <c r="F4" s="34">
+      <c r="F4" s="48">
         <v>13</v>
       </c>
-      <c r="G4" s="36">
+      <c r="G4" s="50">
         <v>10</v>
       </c>
     </row>
@@ -4238,13 +5760,13 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E5" s="32">
+      <c r="E5" s="46">
         <v>12</v>
       </c>
-      <c r="F5" s="34">
+      <c r="F5" s="48">
         <v>11</v>
       </c>
-      <c r="G5" s="36">
+      <c r="G5" s="50">
         <v>9</v>
       </c>
     </row>
@@ -4267,106 +5789,106 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E6" s="32">
+      <c r="E6" s="46">
         <v>32</v>
       </c>
-      <c r="F6" s="34">
+      <c r="F6" s="48">
         <v>29</v>
       </c>
-      <c r="G6" s="36">
+      <c r="G6" s="50">
         <v>23</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="45" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="45" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="45" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="45" t="inlineStr">
         <is>
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E7" s="33">
+      <c r="E7" s="47">
         <v>77</v>
       </c>
-      <c r="F7" s="35">
+      <c r="F7" s="49">
         <v>71</v>
       </c>
-      <c r="G7" s="37">
+      <c r="G7" s="51">
         <v>58</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="45" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="45" t="inlineStr">
         <is>
           <t>TOTAL SUBREGIÓN NORTE</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>NORTE</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="C8" s="45" t="inlineStr">
+        <is>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="D8" s="45" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E8" s="33">
+      <c r="E8" s="47">
         <v>1184</v>
       </c>
-      <c r="F8" s="35">
+      <c r="F8" s="49">
         <v>1056</v>
       </c>
-      <c r="G8" s="37">
+      <c r="G8" s="51">
         <v>1022</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="45" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="45" t="inlineStr">
         <is>
           <t>TOTAL DEPARTAMENTO (ANTIOQUIA)</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="45" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="45" t="inlineStr">
         <is>
           <t>DEPARTAMENTO DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E9" s="33">
+      <c r="E9" s="47">
         <v>27352</v>
       </c>
-      <c r="F9" s="35">
+      <c r="F9" s="49">
         <v>24834</v>
       </c>
-      <c r="G9" s="37">
+      <c r="G9" s="51">
         <v>23637</v>
       </c>
     </row>
@@ -4382,47 +5904,47 @@
   <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="37.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="53" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="53" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="53" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="53" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="53" t="inlineStr">
         <is>
           <t>Número de solicitudes</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="53" t="inlineStr">
         <is>
           <t>Población (2025)</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="53" t="inlineStr">
         <is>
           <t>Tasa de solicitudes (por 1.000 hab.)</t>
         </is>
@@ -4447,13 +5969,13 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E2" s="38">
+      <c r="E2" s="55">
         <v>11</v>
       </c>
-      <c r="F2" s="40">
+      <c r="F2" s="57">
         <v>6151</v>
       </c>
-      <c r="G2" s="42">
+      <c r="G2" s="59">
         <v>1.78832710128434</v>
       </c>
     </row>
@@ -4476,13 +5998,13 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E3" s="38">
+      <c r="E3" s="55">
         <v>9</v>
       </c>
-      <c r="F3" s="40">
+      <c r="F3" s="57">
         <v>19793</v>
       </c>
-      <c r="G3" s="42">
+      <c r="G3" s="59">
         <v>0.454706209265902</v>
       </c>
     </row>
@@ -4505,13 +6027,13 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E4" s="38">
+      <c r="E4" s="55">
         <v>13</v>
       </c>
-      <c r="F4" s="40">
+      <c r="F4" s="57">
         <v>12736</v>
       </c>
-      <c r="G4" s="42">
+      <c r="G4" s="59">
         <v>1.02072864321608</v>
       </c>
     </row>
@@ -4534,13 +6056,13 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E5" s="38">
+      <c r="E5" s="55">
         <v>12</v>
       </c>
-      <c r="F5" s="40">
+      <c r="F5" s="57">
         <v>22287</v>
       </c>
-      <c r="G5" s="42">
+      <c r="G5" s="59">
         <v>0.538430475164894</v>
       </c>
     </row>
@@ -4563,106 +6085,106 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E6" s="38">
+      <c r="E6" s="55">
         <v>32</v>
       </c>
-      <c r="F6" s="40">
+      <c r="F6" s="57">
         <v>40261</v>
       </c>
-      <c r="G6" s="42">
+      <c r="G6" s="59">
         <v>0.794813839695984</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="54" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="54" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="54" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="54" t="inlineStr">
         <is>
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E7" s="39">
+      <c r="E7" s="56">
         <v>77</v>
       </c>
-      <c r="F7" s="41">
+      <c r="F7" s="58">
         <v>101228</v>
       </c>
-      <c r="G7" s="43">
+      <c r="G7" s="60">
         <v>0.760659106176157</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="54" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="54" t="inlineStr">
         <is>
           <t>TOTAL SUBREGIÓN NORTE</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>NORTE</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="C8" s="54" t="inlineStr">
+        <is>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="D8" s="54" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E8" s="39">
+      <c r="E8" s="56">
         <v>1184</v>
       </c>
-      <c r="F8" s="41">
+      <c r="F8" s="58">
         <v>255681</v>
       </c>
-      <c r="G8" s="43">
+      <c r="G8" s="60">
         <v>4.63077037402075</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="54" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="54" t="inlineStr">
         <is>
           <t>TOTAL DEPARTAMENTO (ANTIOQUIA)</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="54" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="54" t="inlineStr">
         <is>
           <t>DEPARTAMENTO DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E9" s="39">
+      <c r="E9" s="56">
         <v>27352</v>
       </c>
-      <c r="F9" s="41">
+      <c r="F9" s="58">
         <v>6821720</v>
       </c>
-      <c r="G9" s="43">
+      <c r="G9" s="60">
         <v>4.00954597960632</v>
       </c>
     </row>
@@ -4678,47 +6200,47 @@
   <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="62" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="62" t="inlineStr">
         <is>
           <t>Periodo</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="62" t="inlineStr">
         <is>
           <t>N respuestas</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="62" t="inlineStr">
         <is>
           <t>Muy seguro (%)</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="62" t="inlineStr">
         <is>
           <t>Seguro (%)</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="62" t="inlineStr">
         <is>
           <t>Inseguro (%)</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="62" t="inlineStr">
         <is>
           <t>Muy inseguro (%)</t>
         </is>
@@ -4735,19 +6257,19 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="C2" s="48">
+      <c r="C2" s="67">
         <v>344</v>
       </c>
-      <c r="D2" s="44">
+      <c r="D2" s="63">
         <v>0.0675601418297848</v>
       </c>
-      <c r="E2" s="45">
+      <c r="E2" s="64">
         <v>0.685130309027178</v>
       </c>
-      <c r="F2" s="46">
+      <c r="F2" s="65">
         <v>0.198617934781808</v>
       </c>
-      <c r="G2" s="47">
+      <c r="G2" s="66">
         <v>0.0486916143612287</v>
       </c>
     </row>
@@ -4762,19 +6284,19 @@
           <t>2019 (1)</t>
         </is>
       </c>
-      <c r="C3" s="48">
+      <c r="C3" s="67">
         <v>344</v>
       </c>
-      <c r="D3" s="44">
+      <c r="D3" s="63">
         <v>0.136523652047281</v>
       </c>
-      <c r="E3" s="45">
+      <c r="E3" s="64">
         <v>0.682440090821911</v>
       </c>
-      <c r="F3" s="46">
+      <c r="F3" s="65">
         <v>0.145725108854342</v>
       </c>
-      <c r="G3" s="47">
+      <c r="G3" s="66">
         <v>0.0353111482764656</v>
       </c>
     </row>
@@ -4789,19 +6311,19 @@
           <t>2019 (2)</t>
         </is>
       </c>
-      <c r="C4" s="48">
+      <c r="C4" s="67">
         <v>336</v>
       </c>
-      <c r="D4" s="44">
+      <c r="D4" s="63">
         <v>0.0961090700618537</v>
       </c>
-      <c r="E4" s="45">
+      <c r="E4" s="64">
         <v>0.758001457119556</v>
       </c>
-      <c r="F4" s="46">
+      <c r="F4" s="65">
         <v>0.110291510742229</v>
       </c>
-      <c r="G4" s="47">
+      <c r="G4" s="66">
         <v>0.0355979620763621</v>
       </c>
     </row>
@@ -4816,19 +6338,19 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="C5" s="48">
+      <c r="C5" s="67">
         <v>216</v>
       </c>
-      <c r="D5" s="44">
+      <c r="D5" s="63">
         <v>0.0677601343323669</v>
       </c>
-      <c r="E5" s="45">
+      <c r="E5" s="64">
         <v>0.745883146498697</v>
       </c>
-      <c r="F5" s="46">
+      <c r="F5" s="65">
         <v>0.173250649134815</v>
       </c>
-      <c r="G5" s="47">
+      <c r="G5" s="66">
         <v>0.0131060700341212</v>
       </c>
     </row>
@@ -4843,19 +6365,19 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="C6" s="48">
+      <c r="C6" s="67">
         <v>272</v>
       </c>
-      <c r="D6" s="44">
+      <c r="D6" s="63">
         <v>0.0707824065531934</v>
       </c>
-      <c r="E6" s="45">
+      <c r="E6" s="64">
         <v>0.780361859680954</v>
       </c>
-      <c r="F6" s="46">
+      <c r="F6" s="65">
         <v>0.141019611660632</v>
       </c>
-      <c r="G6" s="47">
+      <c r="G6" s="66">
         <v>0.00783612210522076</v>
       </c>
     </row>
@@ -4870,19 +6392,19 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="C7" s="48">
+      <c r="C7" s="67">
         <v>272</v>
       </c>
-      <c r="D7" s="44">
+      <c r="D7" s="63">
         <v>0.121434107868613</v>
       </c>
-      <c r="E7" s="45">
+      <c r="E7" s="64">
         <v>0.720848681945732</v>
       </c>
-      <c r="F7" s="46">
+      <c r="F7" s="65">
         <v>0.12331756279583</v>
       </c>
-      <c r="G7" s="47">
+      <c r="G7" s="66">
         <v>0.0343996473898254</v>
       </c>
     </row>
@@ -4897,19 +6419,19 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="C8" s="48">
+      <c r="C8" s="67">
         <v>240</v>
       </c>
-      <c r="D8" s="44">
+      <c r="D8" s="63">
         <v>0.0702898080427005</v>
       </c>
-      <c r="E8" s="45">
+      <c r="E8" s="64">
         <v>0.774056105664931</v>
       </c>
-      <c r="F8" s="46">
+      <c r="F8" s="65">
         <v>0.143702103045247</v>
       </c>
-      <c r="G8" s="47">
+      <c r="G8" s="66">
         <v>0.0119519832471212</v>
       </c>
     </row>
@@ -4924,19 +6446,19 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="C9" s="48">
+      <c r="C9" s="67">
         <v>249</v>
       </c>
-      <c r="D9" s="44">
+      <c r="D9" s="63">
         <v>0.0700259516429931</v>
       </c>
-      <c r="E9" s="45">
+      <c r="E9" s="64">
         <v>0.826434494997797</v>
       </c>
-      <c r="F9" s="46">
+      <c r="F9" s="65">
         <v>0.0828698498366347</v>
       </c>
-      <c r="G9" s="47">
+      <c r="G9" s="66">
         <v>0.0206697035225749</v>
       </c>
     </row>
@@ -4952,47 +6474,47 @@
   <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="69" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="69" t="inlineStr">
         <is>
           <t>Periodo</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="69" t="inlineStr">
         <is>
           <t>N respuestas</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="69" t="inlineStr">
         <is>
           <t>Más seguro (%)</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="69" t="inlineStr">
         <is>
           <t>Menos seguro (%)</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="69" t="inlineStr">
         <is>
           <t>Igual (%)</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="69" t="inlineStr">
         <is>
           <t>No sabe/No responde (%)</t>
         </is>
@@ -5009,19 +6531,19 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="C2" s="53">
+      <c r="C2" s="74">
         <v>344</v>
       </c>
-      <c r="D2" s="49">
+      <c r="D2" s="70">
         <v>0.169651549214151</v>
       </c>
-      <c r="E2" s="50">
+      <c r="E2" s="71">
         <v>0.144357208612453</v>
       </c>
-      <c r="F2" s="51">
+      <c r="F2" s="72">
         <v>0.642776137143313</v>
       </c>
-      <c r="G2" s="52">
+      <c r="G2" s="73">
         <v>0.0432151050300823</v>
       </c>
     </row>
@@ -5036,19 +6558,19 @@
           <t>2019 (1)</t>
         </is>
       </c>
-      <c r="C3" s="53">
+      <c r="C3" s="74">
         <v>344</v>
       </c>
-      <c r="D3" s="49">
+      <c r="D3" s="70">
         <v>0.307946361051725</v>
       </c>
-      <c r="E3" s="50">
+      <c r="E3" s="71">
         <v>0.139008475941576</v>
       </c>
-      <c r="F3" s="51">
+      <c r="F3" s="72">
         <v>0.508254717198475</v>
       </c>
-      <c r="G3" s="52">
+      <c r="G3" s="73">
         <v>0.0447904458082242</v>
       </c>
     </row>
@@ -5063,19 +6585,19 @@
           <t>2019 (2)</t>
         </is>
       </c>
-      <c r="C4" s="53">
+      <c r="C4" s="74">
         <v>336</v>
       </c>
-      <c r="D4" s="49">
+      <c r="D4" s="70">
         <v>0.302259266762212</v>
       </c>
-      <c r="E4" s="50">
+      <c r="E4" s="71">
         <v>0.10751935468985</v>
       </c>
-      <c r="F4" s="51">
+      <c r="F4" s="72">
         <v>0.585534319714311</v>
       </c>
-      <c r="G4" s="52">
+      <c r="G4" s="73">
         <v>0.00468705883362734</v>
       </c>
     </row>
@@ -5090,19 +6612,19 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="C5" s="53">
+      <c r="C5" s="74">
         <v>216</v>
       </c>
-      <c r="D5" s="49">
+      <c r="D5" s="70">
         <v>0.185740072374087</v>
       </c>
-      <c r="E5" s="50">
+      <c r="E5" s="71">
         <v>0.109941614677601</v>
       </c>
-      <c r="F5" s="51">
+      <c r="F5" s="72">
         <v>0.701103863871695</v>
       </c>
-      <c r="G5" s="52">
+      <c r="G5" s="73">
         <v>0.00321444907661701</v>
       </c>
     </row>
@@ -5117,19 +6639,19 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="C6" s="53">
+      <c r="C6" s="74">
         <v>272</v>
       </c>
-      <c r="D6" s="49">
+      <c r="D6" s="70">
         <v>0.147970751929919</v>
       </c>
-      <c r="E6" s="50">
+      <c r="E6" s="71">
         <v>0.0874874841976774</v>
       </c>
-      <c r="F6" s="51">
+      <c r="F6" s="72">
         <v>0.764541763872403</v>
       </c>
-      <c r="G6" s="52">
+      <c r="G6" s="73">
         <v>0</v>
       </c>
     </row>
@@ -5144,19 +6666,19 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="C7" s="53">
+      <c r="C7" s="74">
         <v>272</v>
       </c>
-      <c r="D7" s="49">
+      <c r="D7" s="70">
         <v>0.212443612741505</v>
       </c>
-      <c r="E7" s="50">
+      <c r="E7" s="71">
         <v>0.0723293191309152</v>
       </c>
-      <c r="F7" s="51">
+      <c r="F7" s="72">
         <v>0.714341170667201</v>
       </c>
-      <c r="G7" s="52">
+      <c r="G7" s="73">
         <v>0.000885897460378978</v>
       </c>
     </row>
@@ -5171,19 +6693,19 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="C8" s="53">
+      <c r="C8" s="74">
         <v>240</v>
       </c>
-      <c r="D8" s="49">
+      <c r="D8" s="70">
         <v>0.195488724800149</v>
       </c>
-      <c r="E8" s="50">
+      <c r="E8" s="71">
         <v>0.13960463879758</v>
       </c>
-      <c r="F8" s="51">
+      <c r="F8" s="72">
         <v>0.657542123955844</v>
       </c>
-      <c r="G8" s="52">
+      <c r="G8" s="73">
         <v>0.00736451244642682</v>
       </c>
     </row>
@@ -5198,19 +6720,19 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="C9" s="53">
+      <c r="C9" s="74">
         <v>249</v>
       </c>
-      <c r="D9" s="49">
+      <c r="D9" s="70">
         <v>0.210011321817851</v>
       </c>
-      <c r="E9" s="50">
+      <c r="E9" s="71">
         <v>0.0699138762595573</v>
       </c>
-      <c r="F9" s="51">
+      <c r="F9" s="72">
         <v>0.712957658408463</v>
       </c>
-      <c r="G9" s="52">
+      <c r="G9" s="73">
         <v>0.00711714351412855</v>
       </c>
     </row>
